--- a/qa/REFlect_AI_Test_Report.xlsx
+++ b/qa/REFlect_AI_Test_Report.xlsx
@@ -69,7 +69,7 @@
       <color rgb="009C6500"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -84,6 +84,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -134,6 +139,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -519,7 +527,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-07 13:38</t>
+          <t>Generated 2026-09-07 13:50</t>
         </is>
       </c>
     </row>
@@ -574,7 +582,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -594,7 +602,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -615,7 +623,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>97.8%</t>
         </is>
       </c>
     </row>
@@ -677,7 +685,7 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -763,7 +771,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1682,7 +1690,7 @@
         </is>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.077</v>
+        <v>0.059</v>
       </c>
       <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="7" t="inlineStr">
@@ -1748,7 +1756,7 @@
         </is>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.136</v>
+        <v>0.138</v>
       </c>
       <c r="M14" s="7" t="inlineStr"/>
       <c r="N14" s="7" t="inlineStr">
@@ -1814,7 +1822,7 @@
         </is>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.013</v>
+        <v>0.023</v>
       </c>
       <c r="M15" s="7" t="inlineStr"/>
       <c r="N15" s="7" t="inlineStr">
@@ -1880,7 +1888,7 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.013</v>
+        <v>0.025</v>
       </c>
       <c r="M16" s="7" t="inlineStr"/>
       <c r="N16" s="7" t="inlineStr">
@@ -1946,7 +1954,7 @@
         </is>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="M17" s="7" t="inlineStr"/>
       <c r="N17" s="7" t="inlineStr">
@@ -2012,7 +2020,7 @@
         </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="M18" s="7" t="inlineStr"/>
       <c r="N18" s="7" t="inlineStr">
@@ -2279,7 +2287,7 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.064</v>
+        <v>0.058</v>
       </c>
       <c r="M22" s="7" t="inlineStr"/>
       <c r="N22" s="7" t="inlineStr">
@@ -2336,18 +2344,22 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>0 items, kinds=[]</t>
-        </is>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>0 items; upstream probe HTTP 503</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.496</v>
-      </c>
-      <c r="M23" s="7" t="inlineStr"/>
+        <v>0.911</v>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>('M:\\REFlect_AI\\Impact_Lab\\qa\\test_integration.py', 149, 'Skipped: Google Patents is blocking this host (HTTP 503 anti-bot page). Scraped XHR endpoint, not a supported API - patent evidence will be empty.')</t>
+        </is>
+      </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
           <t>qa/test_integration.py::test_patent_fetcher</t>
@@ -2412,7 +2424,7 @@
         </is>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.819</v>
+        <v>1.17</v>
       </c>
       <c r="M24" s="7" t="inlineStr"/>
       <c r="N24" s="7" t="inlineStr">
@@ -2478,7 +2490,7 @@
         </is>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.023</v>
+        <v>0.013</v>
       </c>
       <c r="M25" s="7" t="inlineStr"/>
       <c r="N25" s="7" t="inlineStr">
@@ -2544,7 +2556,7 @@
         </is>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.022</v>
+        <v>0.026</v>
       </c>
       <c r="M26" s="7" t="inlineStr"/>
       <c r="N26" s="7" t="inlineStr">
@@ -2610,7 +2622,7 @@
         </is>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="M27" s="7" t="inlineStr"/>
       <c r="N27" s="7" t="inlineStr">
@@ -2676,7 +2688,7 @@
         </is>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.023</v>
+        <v>0.025</v>
       </c>
       <c r="M28" s="7" t="inlineStr"/>
       <c r="N28" s="7" t="inlineStr">
@@ -2742,7 +2754,7 @@
         </is>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.012</v>
+        <v>0.023</v>
       </c>
       <c r="M29" s="7" t="inlineStr"/>
       <c r="N29" s="7" t="inlineStr">
@@ -2809,7 +2821,7 @@
         </is>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="M30" s="7" t="inlineStr"/>
       <c r="N30" s="7" t="inlineStr">
@@ -2876,7 +2888,7 @@
         </is>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="M31" s="7" t="inlineStr"/>
       <c r="N31" s="7" t="inlineStr">
@@ -2943,7 +2955,7 @@
         </is>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
       <c r="M32" s="7" t="inlineStr"/>
       <c r="N32" s="7" t="inlineStr">
@@ -3010,7 +3022,7 @@
         </is>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.122</v>
+        <v>0.112</v>
       </c>
       <c r="M33" s="7" t="inlineStr"/>
       <c r="N33" s="7" t="inlineStr">
@@ -3211,7 +3223,7 @@
         </is>
       </c>
       <c r="L36" s="7" t="n">
-        <v>0.144</v>
+        <v>0.628</v>
       </c>
       <c r="M36" s="7" t="inlineStr"/>
       <c r="N36" s="7" t="inlineStr">
@@ -3278,7 +3290,7 @@
         </is>
       </c>
       <c r="L37" s="7" t="n">
-        <v>0.507</v>
+        <v>0.508</v>
       </c>
       <c r="M37" s="7" t="inlineStr"/>
       <c r="N37" s="7" t="inlineStr">
@@ -3345,7 +3357,7 @@
         </is>
       </c>
       <c r="L38" s="7" t="n">
-        <v>0.106</v>
+        <v>0.1</v>
       </c>
       <c r="M38" s="7" t="inlineStr"/>
       <c r="N38" s="7" t="inlineStr">
@@ -3403,7 +3415,7 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>mean=15.9 ms, max=22.5 ms over 5 calls</t>
+          <t>mean=13.8 ms, max=22.9 ms over 5 calls</t>
         </is>
       </c>
       <c r="K39" s="9" t="inlineStr">
@@ -3412,7 +3424,7 @@
         </is>
       </c>
       <c r="L39" s="7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M39" s="7" t="inlineStr"/>
       <c r="N39" s="7" t="inlineStr">
@@ -3469,7 +3481,7 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>0.08 s to loaded</t>
+          <t>0.13 s to loaded</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">
@@ -3478,7 +3490,7 @@
         </is>
       </c>
       <c r="L40" s="7" t="n">
-        <v>0.08</v>
+        <v>0.128</v>
       </c>
       <c r="M40" s="7" t="inlineStr"/>
       <c r="N40" s="7" t="inlineStr">
@@ -3536,7 +3548,7 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>0.0001 ms per cache hit</t>
+          <t>0.0002 ms per cache hit</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr">
@@ -3545,7 +3557,7 @@
         </is>
       </c>
       <c r="L41" s="7" t="n">
-        <v>0.093</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="M41" s="7" t="inlineStr"/>
       <c r="N41" s="7" t="inlineStr">
@@ -3603,7 +3615,7 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>20 concurrent in 0.08s, non-200=0</t>
+          <t>20 concurrent in 0.09s, non-200=0</t>
         </is>
       </c>
       <c r="K42" s="9" t="inlineStr">
@@ -3612,7 +3624,7 @@
         </is>
       </c>
       <c r="L42" s="7" t="n">
-        <v>0.079</v>
+        <v>0.094</v>
       </c>
       <c r="M42" s="7" t="inlineStr"/>
       <c r="N42" s="7" t="inlineStr">
@@ -3678,7 +3690,7 @@
         </is>
       </c>
       <c r="L43" s="7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="M43" s="7" t="inlineStr"/>
       <c r="N43" s="7" t="inlineStr">
@@ -3803,7 +3815,7 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>scanned 20822 bytes across 3 endpoints; leaks=none</t>
+          <t>scanned 20837 bytes across 3 endpoints; leaks=none</t>
         </is>
       </c>
       <c r="K45" s="9" t="inlineStr">
@@ -3812,7 +3824,7 @@
         </is>
       </c>
       <c r="L45" s="7" t="n">
-        <v>0.057</v>
+        <v>0.064</v>
       </c>
       <c r="M45" s="7" t="inlineStr"/>
       <c r="N45" s="7" t="inlineStr">
@@ -3879,7 +3891,7 @@
         </is>
       </c>
       <c r="L46" s="7" t="n">
-        <v>0.904</v>
+        <v>0.905</v>
       </c>
       <c r="M46" s="7" t="inlineStr"/>
       <c r="N46" s="7" t="inlineStr">
@@ -3945,7 +3957,7 @@
         </is>
       </c>
       <c r="L47" s="7" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="M47" s="7" t="inlineStr"/>
       <c r="N47" s="7" t="inlineStr">
@@ -4030,47 +4042,48 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DEF-001</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TC-I-011</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>P1 - High</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Fetchers</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>No defects open. All executed cases passed.</t>
+          <t>Patent fetcher executes without error</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Returns a list without raising; any items carry kind='patent'.</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 items; upstream probe HTTP 503
+('M:\\REFlect_AI\\Impact_Lab\\qa\\test_integration.py', 149, 'Skipped: Google Patents is blocking this host (HTTP 503 anti-bot page). Scraped XHR endpoint, not a supported API - patent evidence will be empty.')</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>

--- a/qa/REFlect_AI_Test_Report.xlsx
+++ b/qa/REFlect_AI_Test_Report.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Demo Checks" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$N$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$N$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,7 +45,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006100"/>
+      <color rgb="009C0006"/>
       <sz val="12"/>
     </font>
     <font>
@@ -69,7 +69,7 @@
       <color rgb="009C6500"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +89,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -141,6 +146,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -527,7 +535,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-07 13:50</t>
+          <t>Generated 2026-09-07 13:56</t>
         </is>
       </c>
     </row>
@@ -539,7 +547,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>GO - no blocking defects</t>
+          <t>REVIEW - 1 non-blocking failure(s)</t>
         </is>
       </c>
     </row>
@@ -562,7 +570,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -572,7 +580,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -582,7 +590,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -592,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -623,7 +631,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>96.7%</t>
         </is>
       </c>
     </row>
@@ -752,10 +760,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C23" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -768,13 +776,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C24" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -784,10 +792,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -804,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1690,7 +1698,7 @@
         </is>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.059</v>
+        <v>0.058</v>
       </c>
       <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="7" t="inlineStr">
@@ -1756,7 +1764,7 @@
         </is>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.138</v>
+        <v>0.129</v>
       </c>
       <c r="M14" s="7" t="inlineStr"/>
       <c r="N14" s="7" t="inlineStr">
@@ -1822,7 +1830,7 @@
         </is>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.023</v>
+        <v>0.014</v>
       </c>
       <c r="M15" s="7" t="inlineStr"/>
       <c r="N15" s="7" t="inlineStr">
@@ -1888,7 +1896,7 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
       <c r="M16" s="7" t="inlineStr"/>
       <c r="N16" s="7" t="inlineStr">
@@ -1954,7 +1962,7 @@
         </is>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.013</v>
+        <v>0.025</v>
       </c>
       <c r="M17" s="7" t="inlineStr"/>
       <c r="N17" s="7" t="inlineStr">
@@ -2287,7 +2295,7 @@
         </is>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.058</v>
+        <v>0.052</v>
       </c>
       <c r="M22" s="7" t="inlineStr"/>
       <c r="N22" s="7" t="inlineStr">
@@ -2353,7 +2361,7 @@
         </is>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.911</v>
+        <v>0.836</v>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
@@ -2424,7 +2432,7 @@
         </is>
       </c>
       <c r="L24" s="7" t="n">
-        <v>1.17</v>
+        <v>0.976</v>
       </c>
       <c r="M24" s="7" t="inlineStr"/>
       <c r="N24" s="7" t="inlineStr">
@@ -2490,7 +2498,7 @@
         </is>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.013</v>
+        <v>0.023</v>
       </c>
       <c r="M25" s="7" t="inlineStr"/>
       <c r="N25" s="7" t="inlineStr">
@@ -2556,7 +2564,7 @@
         </is>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.026</v>
+        <v>0.022</v>
       </c>
       <c r="M26" s="7" t="inlineStr"/>
       <c r="N26" s="7" t="inlineStr">
@@ -2613,7 +2621,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>HTTP 401</t>
+          <t>HTTP 422</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
@@ -2622,7 +2630,7 @@
         </is>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="M27" s="7" t="inlineStr"/>
       <c r="N27" s="7" t="inlineStr">
@@ -2688,7 +2696,7 @@
         </is>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.025</v>
+        <v>0.013</v>
       </c>
       <c r="M28" s="7" t="inlineStr"/>
       <c r="N28" s="7" t="inlineStr">
@@ -2754,7 +2762,7 @@
         </is>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.023</v>
+        <v>0.012</v>
       </c>
       <c r="M29" s="7" t="inlineStr"/>
       <c r="N29" s="7" t="inlineStr">
@@ -2888,7 +2896,7 @@
         </is>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.026</v>
+        <v>0.029</v>
       </c>
       <c r="M31" s="7" t="inlineStr"/>
       <c r="N31" s="7" t="inlineStr">
@@ -2955,7 +2963,7 @@
         </is>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.054</v>
+        <v>0.052</v>
       </c>
       <c r="M32" s="7" t="inlineStr"/>
       <c r="N32" s="7" t="inlineStr">
@@ -3022,7 +3030,7 @@
         </is>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.112</v>
+        <v>0.614</v>
       </c>
       <c r="M33" s="7" t="inlineStr"/>
       <c r="N33" s="7" t="inlineStr">
@@ -3089,7 +3097,7 @@
         </is>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="M34" s="7" t="inlineStr"/>
       <c r="N34" s="7" t="inlineStr">
@@ -3223,7 +3231,7 @@
         </is>
       </c>
       <c r="L36" s="7" t="n">
-        <v>0.628</v>
+        <v>0.63</v>
       </c>
       <c r="M36" s="7" t="inlineStr"/>
       <c r="N36" s="7" t="inlineStr">
@@ -3290,7 +3298,7 @@
         </is>
       </c>
       <c r="L37" s="7" t="n">
-        <v>0.508</v>
+        <v>0.599</v>
       </c>
       <c r="M37" s="7" t="inlineStr"/>
       <c r="N37" s="7" t="inlineStr">
@@ -3415,7 +3423,7 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>mean=13.8 ms, max=22.9 ms over 5 calls</t>
+          <t>mean=14.0 ms, max=22.2 ms over 5 calls</t>
         </is>
       </c>
       <c r="K39" s="9" t="inlineStr">
@@ -3481,7 +3489,7 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>0.13 s to loaded</t>
+          <t>0.07 s to loaded</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">
@@ -3490,7 +3498,7 @@
         </is>
       </c>
       <c r="L40" s="7" t="n">
-        <v>0.128</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="M40" s="7" t="inlineStr"/>
       <c r="N40" s="7" t="inlineStr">
@@ -3548,7 +3556,7 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>0.0002 ms per cache hit</t>
+          <t>0.0001 ms per cache hit</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr">
@@ -3557,7 +3565,7 @@
         </is>
       </c>
       <c r="L41" s="7" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="M41" s="7" t="inlineStr"/>
       <c r="N41" s="7" t="inlineStr">
@@ -3615,7 +3623,7 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>20 concurrent in 0.09s, non-200=0</t>
+          <t>20 concurrent in 0.10s, non-200=0</t>
         </is>
       </c>
       <c r="K42" s="9" t="inlineStr">
@@ -3624,7 +3632,7 @@
         </is>
       </c>
       <c r="L42" s="7" t="n">
-        <v>0.094</v>
+        <v>0.098</v>
       </c>
       <c r="M42" s="7" t="inlineStr"/>
       <c r="N42" s="7" t="inlineStr">
@@ -3690,7 +3698,7 @@
         </is>
       </c>
       <c r="L43" s="7" t="n">
-        <v>0.05</v>
+        <v>0.075</v>
       </c>
       <c r="M43" s="7" t="inlineStr"/>
       <c r="N43" s="7" t="inlineStr">
@@ -3757,7 +3765,7 @@
         </is>
       </c>
       <c r="L44" s="7" t="n">
-        <v>0.026</v>
+        <v>0.043</v>
       </c>
       <c r="M44" s="7" t="inlineStr"/>
       <c r="N44" s="7" t="inlineStr">
@@ -3815,7 +3823,7 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>scanned 20837 bytes across 3 endpoints; leaks=none</t>
+          <t>scanned 20823 bytes across 3 endpoints; leaks=none</t>
         </is>
       </c>
       <c r="K45" s="9" t="inlineStr">
@@ -3824,7 +3832,7 @@
         </is>
       </c>
       <c r="L45" s="7" t="n">
-        <v>0.064</v>
+        <v>0.057</v>
       </c>
       <c r="M45" s="7" t="inlineStr"/>
       <c r="N45" s="7" t="inlineStr">
@@ -3891,7 +3899,7 @@
         </is>
       </c>
       <c r="L46" s="7" t="n">
-        <v>0.905</v>
+        <v>0.885</v>
       </c>
       <c r="M46" s="7" t="inlineStr"/>
       <c r="N46" s="7" t="inlineStr">
@@ -3957,7 +3965,7 @@
         </is>
       </c>
       <c r="L47" s="7" t="n">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
       <c r="M47" s="7" t="inlineStr"/>
       <c r="N47" s="7" t="inlineStr">
@@ -3966,8 +3974,1027 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-001</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Token forgery</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Token forged with the shipped default secret is rejected</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>P0 - Blocker</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>auth.py falls back to LINKEDIN_JWT_SECRET='change-me-in-production' when unset.</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>1. Mint a JWT signed with the known default secret.
+2. Call a protected endpoint with it.</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>401/403. If accepted, the deployment is using the public default secret and anyone can mint an admin token.</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>forged-with-default-secret -&gt; HTTP 401; configured secret is default=False</t>
+        </is>
+      </c>
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="M48" s="7" t="inlineStr"/>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_default_secret_not_in_use</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-002</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Token forgery</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>alg=none token is rejected</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>P0 - Blocker</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Backend uses HS256.</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>1. Craft an unsigned JWT with header alg=none.
+2. Call a protected endpoint with it.</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>401/403 - the decoder must pin the algorithm and refuse unsigned tokens.</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>alg=none -&gt; HTTP 401</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="M49" s="7" t="inlineStr"/>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_alg_none_rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-003</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Token forgery</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Signature-stripped token is rejected</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>P0 - Blocker</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>A valid token.</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>1. Remove the signature segment, keeping header and payload.
+2. Call a protected endpoint.</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>401/403.</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>signature stripped -&gt; HTTP 401</t>
+        </is>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="M50" s="7" t="inlineStr"/>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_signature_stripped_rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-004</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Token forgery</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Token signed with an attacker-chosen secret is rejected</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>P0 - Blocker</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Attacker does not know the server secret.</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>1. Sign a well-formed payload with an arbitrary secret.
+2. Call a protected endpoint.</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>401/403 - signature verification fails.</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>attacker-signed -&gt; HTTP 401</t>
+        </is>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="M51" s="7" t="inlineStr"/>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_wrong_secret_rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-005</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Session lifetime</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Issued tokens carry an expiry claim</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>create_orcid_token() builds the session JWT.</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>1. Mint a token.
+2. Decode it and inspect the claims for 'exp'.</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>An 'exp' claim is present. Without it a leaked token is valid forever and cannot be revoked.</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>claims=['email', 'name', 'orcid', 'provider', 'uid']</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>record = &lt;function record.&lt;locals&gt;._record at 0x0000023B322B1620&gt;
+    @pytest.mark.case("TC-S-005")
+    def test_token_has_expiry(record):
+        token = create_orcid_token(uid="u", email="e@x.test", name="N", orcid="0000")
+        claims = pyjwt.decode(token, LINKEDIN_JWT_SECRET, algorithms=[LINKEDIN_JWT_ALG])
+        record(f"claims={sorted(claims)}")
+&gt;       assert "exp" in claims, (
+            "session tokens carry no exp claim - a leaked token stays valid forever and cannot expire"
+        )
+E       AssertionError: session tokens carry no exp claim - a leaked token stays valid forever and cannot expire
+E       assert 'exp' in {'uid': 'u', 'email': 'e@x.test', 'name': 'N', 'orcid': '0000', ...}
+qa\test_security.py:77: AssertionError</t>
+        </is>
+      </c>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_token_has_expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-006</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Session lifetime</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>An expired token is rejected</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>A token whose exp is in the past.</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>1. Mint a token with exp set to the past.
+2. Call a protected endpoint.</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>401/403 - expiry is enforced at verification time.</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>expired token -&gt; HTTP 401</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="M53" s="7" t="inlineStr"/>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_expired_token_rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-007</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Access control</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>History is scoped to the caller and cannot be pivoted to another user</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>P0 - Blocker</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Two distinct user tokens.</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>1. Request /api/history as user A with a uid query parameter naming user B.
+2. Inspect the uid in the response.</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>The response is scoped to the token's own uid; the query parameter cannot override it (no IDOR).</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200, uid in body=qa-user</t>
+        </is>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L54" s="7" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="M54" s="7" t="inlineStr"/>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_history_not_pivotable</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-008</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Data exposure</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Unauthenticated dataset export does not leak per-user identifiers</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>/api/dataset is declared without an auth dependency.</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>1. GET /api/dataset with no token.
+2. Scan the payload for uid, email or ORCID identifiers.</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>Either the endpoint requires auth, or the exported rows carry no per-user identifiers.</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200, 138237 bytes, identifier fields present=none</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="M55" s="7" t="inlineStr"/>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_dataset_no_user_identifiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-009</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Access control</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Expensive LLM endpoints are not reachable anonymously</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>No token.</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>1. POST /api/analyze, /api/compose, /api/evaluate and /api/ref/beta with no token.</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>Every one returns 401/403 - no anonymous consumption of paid inference.</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>{'/api/analyze': 401, '/api/compose': 401, '/api/evaluate': 401, '/api/ref/beta': 401}</t>
+        </is>
+      </c>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="M56" s="7" t="inlineStr"/>
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_llm_endpoints_need_auth</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-010</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Path traversal payloads do not reach the filesystem</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Backend up.</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>1. Submit ../../ traversal sequences to the search endpoint.
+2. Inspect the response for file content.</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>Treated as an opaque string; no filesystem content and no 500.</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>{'../../../../etc/pa': 422, '....//....//etc/pa': 422, '%2e%2e%2fetc%2fpas': 200}</t>
+        </is>
+      </c>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="n">
+        <v>6.537</v>
+      </c>
+      <c r="M57" s="7" t="inlineStr"/>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_path_traversal</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-011</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Script payloads are not reflected unescaped</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Backend up.</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>1. Submit a script tag as the query.
+2. Inspect the raw response body.</t>
+        </is>
+      </c>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>No executable script echoed into an HTML response context.</t>
+        </is>
+      </c>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 422, content-type=application/json, reflected_in_html=False</t>
+        </is>
+      </c>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="M58" s="7" t="inlineStr"/>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_no_unescaped_script_reflection</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-012</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Injection</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Deeply nested JSON does not exhaust the parser</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>P2 - Medium</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Valid token.</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>1. POST a deeply nested JSON object.
+2. Re-check /health.</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>Bounded 4xx response and the service stays healthy.</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>nested -&gt; 422; health after -&gt; 200</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="M59" s="7" t="inlineStr"/>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_deeply_nested_json</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-013</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Rate limiting</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Sustained request bursts are throttled</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>rate_limit() is wired to the search endpoint at 20 req / 60 s.</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>1. Issue requests past the configured limit from one IP.
+2. Observe the status codes.</t>
+        </is>
+      </c>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>429 Too Many Requests once the limit is exceeded.</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>9 requests, throttled at #9</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L60" s="7" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M60" s="7" t="inlineStr"/>
+      <c r="N60" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_rate_limiting</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-014</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Error handling</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Server errors do not leak stack traces or internal paths</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Backend up.</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>1. Provoke error responses across several endpoints.
+2. Scan bodies for tracebacks and filesystem paths.</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>No 'Traceback', module paths or internal file locations in any response body.</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>scanned 346 bytes; leak markers=none</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="M61" s="7" t="inlineStr"/>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_no_stack_traces</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-015</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>CORS</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>CORS does not combine a wildcard origin with credentials</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Backend up.</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>1. Send a preflight from an arbitrary attacker origin.
+2. Inspect the allow-origin and allow-credentials headers.</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>An arbitrary origin is not reflected alongside allow-credentials: true.</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>attacker origin -&gt; allow-origin='', allow-credentials='true'</t>
+        </is>
+      </c>
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="M62" s="7" t="inlineStr"/>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>qa/test_security.py::test_cors_not_wildcard_with_credentials</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N47"/>
+  <autoFilter ref="A1:N62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3978,7 +5005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4082,6 +5109,65 @@
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>DEF-002</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>TC-S-005</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>P1 - High</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Session lifetime</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Issued tokens carry an expiry claim</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>An 'exp' claim is present. Without it a leaked token is valid forever and cannot be revoked.</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>claims=['email', 'name', 'orcid', 'provider', 'uid']
+record = &lt;function record.&lt;locals&gt;._record at 0x0000023B322B1620&gt;
+    @pytest.mark.case("TC-S-005")
+    def test_token_has_expiry(record):
+        token = create_orcid_token(uid="u", email="e@x.test", name="N", orcid="0000")
+        claims = pyjwt.decode(token, LINKEDIN_JWT_SECRET, algorithms=[LINKEDIN_JWT_ALG])
+        record(f"claims={sorted(claims)}")
+&gt;       assert "exp" in claims, (
+            "session tokens carry no exp claim - a leaked token stays valid forever and cannot expire"
+        )
+E       AssertionError: session tokens carry no exp claim - a leaked token stays valid forever and cannot expire
+E       assert 'exp' in {'uid': 'u', 'email': 'e@x.test', 'name': 'N', 'orcid': '0000', ...}
+qa\test_security.py:77: AssertionError</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
